--- a/AtchisonRegime/Outputs/Euro/MSCI_France/df_regEquityReturns_MSCI_France.xlsx
+++ b/AtchisonRegime/Outputs/Euro/MSCI_France/df_regEquityReturns_MSCI_France.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19282,7 +19282,7 @@
         <v>-1.173508054480522</v>
       </c>
       <c r="C331" t="n">
-        <v>0.07440878746934976</v>
+        <v>0.003059559528599793</v>
       </c>
       <c r="D331" t="b">
         <v>0</v>
@@ -19339,7 +19339,7 @@
         <v>-1.176877030846902</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0780392389232072</v>
+        <v>0.06963252061712617</v>
       </c>
       <c r="D332" t="b">
         <v>0</v>
@@ -19396,7 +19396,7 @@
         <v>-1.162274350584444</v>
       </c>
       <c r="C333" t="n">
-        <v>0.07326265395948543</v>
+        <v>0.06271089526937522</v>
       </c>
       <c r="D333" t="b">
         <v>0</v>
@@ -19453,7 +19453,7 @@
         <v>-1.192124318497693</v>
       </c>
       <c r="C334" t="n">
-        <v>0.05790582692168544</v>
+        <v>0.04690694013080018</v>
       </c>
       <c r="D334" t="b">
         <v>0</v>
@@ -19510,7 +19510,7 @@
         <v>-1.247901006063838</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.05170998467301801</v>
+        <v>0.03049422547834524</v>
       </c>
       <c r="D335" t="b">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>-1.274041300528749</v>
       </c>
       <c r="C336" t="n">
-        <v>0.01934764035298829</v>
+        <v>0.02255665395177126</v>
       </c>
       <c r="D336" t="b">
         <v>0</v>
@@ -19624,7 +19624,7 @@
         <v>-1.224213763458834</v>
       </c>
       <c r="C337" t="n">
-        <v>0.03207639871494124</v>
+        <v>0.02775436740155613</v>
       </c>
       <c r="D337" t="b">
         <v>0</v>
@@ -19681,7 +19681,7 @@
         <v>-1.100583367531713</v>
       </c>
       <c r="C338" t="n">
-        <v>0.04710340453708419</v>
+        <v>0.04565116666107294</v>
       </c>
       <c r="D338" t="b">
         <v>0</v>
@@ -19738,7 +19738,7 @@
         <v>-1.004917433510945</v>
       </c>
       <c r="C339" t="n">
-        <v>0.08885128292497106</v>
+        <v>0.07696715706128913</v>
       </c>
       <c r="D339" t="b">
         <v>0</v>
@@ -19792,10 +19792,10 @@
         <v>45716</v>
       </c>
       <c r="B340" t="n">
-        <v>-0.9279394482883139</v>
+        <v>-0.9466589205079275</v>
       </c>
       <c r="C340" t="n">
-        <v>0.1314508553617306</v>
+        <v>0.1053591485320955</v>
       </c>
       <c r="D340" t="b">
         <v>0</v>
@@ -19849,10 +19849,10 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.8870883778336536</v>
+        <v>-0.9152014981959544</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1564856013311842</v>
+        <v>0.08969259728684205</v>
       </c>
       <c r="D341" t="b">
         <v>0</v>
@@ -19898,6 +19898,63 @@
         <v>211.1100868954314</v>
       </c>
       <c r="Q341" t="n">
+        <v>55.52098716694836</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.8970238361805523</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.07001454885654049</v>
+      </c>
+      <c r="D342" t="b">
+        <v>0</v>
+      </c>
+      <c r="E342" t="b">
+        <v>1</v>
+      </c>
+      <c r="F342" t="n">
+        <v>-0.281037070481904</v>
+      </c>
+      <c r="G342" t="n">
+        <v>729803.1706941209</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>-0.281037070481904</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" t="n">
+        <v>589.8267931493561</v>
+      </c>
+      <c r="O342" t="n">
+        <v>101.9433484861735</v>
+      </c>
+      <c r="P342" t="n">
+        <v>211.1100868954314</v>
+      </c>
+      <c r="Q342" t="n">
         <v>55.52098716694836</v>
       </c>
     </row>
